--- a/data/trans_camb/IP1020-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,32</t>
+          <t>-3,1; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 5,31</t>
+          <t>-2,31; 4,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,46</t>
+          <t>-0,62; 7,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,35</t>
+          <t>-0,62; 3,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,11</t>
+          <t>0,47; 7,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,99</t>
+          <t>0,14; 6,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,3</t>
+          <t>-1,58; 2,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,73</t>
+          <t>-0,26; 4,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,24</t>
+          <t>0,46; 5,59</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,17; —</t>
+          <t>-58,45; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,92; 562,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 1242,87</t>
+          <t>-27,13; 1016,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1098,53</t>
+          <t>-8,79; 1188,06</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,75</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,16</t>
+          <t>1,23; 7,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,0</t>
+          <t>-2,86; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,13</t>
+          <t>-0,18; 5,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,53</t>
+          <t>-0,56; 5,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,82</t>
+          <t>-0,16; 2,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,91</t>
+          <t>-0,25; 2,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,46</t>
+          <t>1,04; 5,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,52</t>
+          <t>-2,6; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,0</t>
+          <t>-6,88; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,82</t>
+          <t>-2,29; 6,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,16</t>
+          <t>-2,77; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,43</t>
+          <t>-2,21; 3,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,87</t>
+          <t>-1,37; 7,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,28</t>
+          <t>-1,77; 2,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,8</t>
+          <t>-2,04; 1,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,87</t>
+          <t>-0,6; 5,27</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 920,02</t>
+          <t>-57,68; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,85</t>
+          <t>0,36; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,28</t>
+          <t>0,39; 3,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,43</t>
+          <t>0,94; 5,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,25</t>
+          <t>-1,73; 1,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,96</t>
+          <t>-2,33; 0,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,1</t>
+          <t>0,11; 5,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,08</t>
+          <t>-0,4; 2,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,83</t>
+          <t>-0,42; 1,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,18</t>
+          <t>1,0; 4,42</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 1341,51</t>
+          <t>-42,83; 1268,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 852,64</t>
+          <t>-49,42; 953,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 812,97</t>
+          <t>-47,76; 727,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,74; 1912,2</t>
+          <t>37,21; 1685,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,67</t>
+          <t>-0,3; 4,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,21</t>
+          <t>-1,59; 2,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,97</t>
+          <t>0,11; 5,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,77</t>
+          <t>-1,46; 3,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,82</t>
+          <t>-2,1; 1,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,9</t>
+          <t>-0,65; 4,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,26</t>
+          <t>-0,12; 3,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,48</t>
+          <t>-1,29; 1,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,21</t>
+          <t>0,18; 4,18</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,86; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 927,17</t>
+          <t>-42,77; 1168,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 1300,47</t>
+          <t>-16,44; 1295,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 10,7</t>
+          <t>-1,37; 10,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,11</t>
+          <t>-3,79; 2,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 7,97</t>
+          <t>-2,72; 8,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,15</t>
+          <t>0,62; 7,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,58</t>
+          <t>0,93; 8,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,04</t>
+          <t>1,25; 11,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,18; 6,44</t>
+          <t>0,27; 6,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,55</t>
+          <t>-0,98; 3,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,18</t>
+          <t>0,25; 7,44</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-56,68; —</t>
+          <t>-28,0; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,26; —</t>
+          <t>-44,33; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,79</t>
+          <t>0,48; 2,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,32</t>
+          <t>-0,42; 1,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,94</t>
+          <t>1,21; 3,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,3</t>
+          <t>-0,54; 1,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,98</t>
+          <t>-0,08; 1,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,63</t>
+          <t>1,19; 3,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,78</t>
+          <t>0,3; 1,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,32</t>
+          <t>-0,01; 1,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,3</t>
+          <t>1,54; 3,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,61; 593,12</t>
+          <t>16,99; 657,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 295,92</t>
+          <t>-47,29; 293,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>78,6; 784,69</t>
+          <t>72,35; 740,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 249,14</t>
+          <t>-47,3; 255,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 419,62</t>
+          <t>-12,65; 416,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>78,59; 750,55</t>
+          <t>76,88; 773,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,89; 300,32</t>
+          <t>20,57; 317,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 246,35</t>
+          <t>-0,97; 267,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>116,57; 551,63</t>
+          <t>124,4; 591,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,29</t>
+          <t>-3,08; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,76</t>
+          <t>-2,06; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,56</t>
+          <t>-0,75; 7,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,61</t>
+          <t>-1,03; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,43</t>
+          <t>0,48; 7,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,07</t>
+          <t>0,23; 6,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,01</t>
+          <t>-1,48; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,76</t>
+          <t>-0,06; 4,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,59</t>
+          <t>0,37; 5,48</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,45; —</t>
+          <t>-55,52; 1193,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,92; 562,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 1016,5</t>
+          <t>-31,38; 1182,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1188,06</t>
+          <t>-3,72; 1241,9</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,91</t>
+          <t>0,73; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,78</t>
+          <t>1,08; 8,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-3,06; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,34</t>
+          <t>-0,51; 5,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,67</t>
+          <t>-0,36; 6,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,91</t>
+          <t>-0,27; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,98</t>
+          <t>-0,25; 2,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,47</t>
+          <t>1,05; 5,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,55</t>
+          <t>-2,27; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,0</t>
+          <t>-5,02; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,58</t>
+          <t>-2,3; 5,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,5</t>
+          <t>-2,75; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,96</t>
+          <t>-2,06; 4,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,2</t>
+          <t>-1,34; 7,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,25</t>
+          <t>-1,82; 2,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,78</t>
+          <t>-2,15; 2,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,27</t>
+          <t>-0,87; 4,71</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,68; —</t>
+          <t>-69,92; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,1</t>
+          <t>0,33; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,61</t>
+          <t>0,29; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,31</t>
+          <t>1,05; 5,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,28</t>
+          <t>-1,57; 1,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,94</t>
+          <t>-1,99; 0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,02</t>
+          <t>0,33; 5,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,05</t>
+          <t>-0,27; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,73</t>
+          <t>-0,39; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,42</t>
+          <t>1,03; 4,32</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 1268,18</t>
+          <t>-19,77; 1564,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 953,35</t>
+          <t>-43,67; 990,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 727,8</t>
+          <t>-50,41; 874,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,21; 1685,15</t>
+          <t>79,61; 1986,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,66</t>
+          <t>-0,44; 4,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,13</t>
+          <t>-2,05; 2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,94</t>
+          <t>-0,02; 6,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,71</t>
+          <t>-1,04; 3,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,42</t>
+          <t>-2,21; 1,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,46</t>
+          <t>-0,67; 4,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,36</t>
+          <t>-0,2; 3,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,3</t>
+          <t>-1,22; 1,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,18</t>
+          <t>0,18; 4,17</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-70,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 1168,44</t>
+          <t>-38,84; 1105,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 1295,57</t>
+          <t>-16,32; inf</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,68</t>
+          <t>-1,23; 10,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,3</t>
+          <t>-4,45; 2,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,66</t>
+          <t>-2,6; 7,82</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,72</t>
+          <t>0,61; 7,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,66</t>
+          <t>0,93; 7,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,36</t>
+          <t>1,38; 10,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,4</t>
+          <t>0,23; 6,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,95</t>
+          <t>-0,95; 4,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,25; 7,44</t>
+          <t>0,32; 7,4</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,0; —</t>
+          <t>-38,45; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,33; —</t>
+          <t>-62,86; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,87</t>
+          <t>0,57; 2,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,38</t>
+          <t>-0,49; 1,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,73</t>
+          <t>1,22; 4,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,23</t>
+          <t>-0,5; 1,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,91</t>
+          <t>-0,13; 1,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,69</t>
+          <t>1,24; 3,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,78</t>
+          <t>0,33; 1,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,39</t>
+          <t>-0,03; 1,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,34</t>
+          <t>1,53; 3,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,99; 657,66</t>
+          <t>21,43; 619,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 293,96</t>
+          <t>-40,44; 342,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>72,35; 740,47</t>
+          <t>76,01; 914,07</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 255,2</t>
+          <t>-46,28; 264,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 416,3</t>
+          <t>-22,02; 384,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>76,88; 773,27</t>
+          <t>75,66; 721,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,57; 317,53</t>
+          <t>22,29; 309,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 267,72</t>
+          <t>-7,37; 225,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>124,4; 591,52</t>
+          <t>118,77; 538,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,97</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,13</t>
+          <t>-0,62; 4,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,04</t>
+          <t>0,09; 7,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 7,22</t>
+          <t>0,43; 7,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,7</t>
+          <t>-3,11; 2,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,53</t>
+          <t>-2,14; 5,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,21</t>
+          <t>-0,35; 8,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,1</t>
+          <t>-1,52; 2,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,87</t>
+          <t>-0,17; 4,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,48</t>
+          <t>0,61; 6,01</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>134,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>488,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>483,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-27,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>56,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>162,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>134,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>488,42%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>424,84%</t>
+          <t>183,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>214,55%</t>
+          <t>247,26%</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-55,52; 1193,02</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-32,3; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 1182,1</t>
+          <t>-23,13; 1242,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1241,9</t>
+          <t>0,54; 1207,46</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,77</t>
+          <t>-3,08; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,44; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,31</t>
+          <t>-0,44; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,0</t>
+          <t>0,72; 5,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,28</t>
+          <t>1,24; 8,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,73</t>
+          <t>-0,17; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,68</t>
+          <t>-0,25; 2,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,2</t>
+          <t>1,04; 5,6</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>282,01%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>324,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>282,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>324,08%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>314,9%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>964,66%</t>
+          <t>989,15%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,72</t>
+          <t>-2,76; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,0</t>
+          <t>-2,09; 4,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,9</t>
+          <t>-1,36; 8,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,5</t>
+          <t>-2,65; 4,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,11</t>
+          <t>-6,33; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,44</t>
+          <t>-2,52; 5,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,25</t>
+          <t>-1,85; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,03</t>
+          <t>-2,12; 1,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,71</t>
+          <t>-0,95; 5,08</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-46,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34,83%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>130,65%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>105,97%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106,32%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-46,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34,83%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>127,72%</t>
+          <t>110,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>117,41%</t>
+          <t>118,81%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,92; —</t>
+          <t>-80,32; 1012,85</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,59</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,1</t>
+          <t>-1,75; 1,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,29</t>
+          <t>-2,0; 0,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,46</t>
+          <t>0,2; 5,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,43</t>
+          <t>0,37; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,97</t>
+          <t>0,18; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,3</t>
+          <t>1,41; 6,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,16</t>
+          <t>-0,25; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,79</t>
+          <t>-0,35; 1,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,32</t>
+          <t>1,26; 4,81</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-36,1%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>249,15%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>609,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>542,02%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>893,66%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,05%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-36,1%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>230,42%</t>
+          <t>1158,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>378,48%</t>
+          <t>451,59%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,04; 1452,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 1564,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 990,74</t>
+          <t>-43,94; 852,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 874,49</t>
+          <t>-45,24; 812,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79,61; 1986,46</t>
+          <t>70,28; 2385,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,45</t>
+          <t>-1,07; 3,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,41</t>
+          <t>-2,38; 1,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,35</t>
+          <t>-0,45; 5,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,74</t>
+          <t>-0,38; 4,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,79</t>
+          <t>-1,6; 2,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,69</t>
+          <t>0,05; 5,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,2</t>
+          <t>-0,26; 3,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,45</t>
+          <t>-1,21; 1,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,17</t>
+          <t>0,14; 4,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>103,69%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-8,71%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>155,92%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>269,14%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>54,75%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>358,19%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>103,69%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,71%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>156,31%</t>
+          <t>328,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>226,74%</t>
+          <t>217,41%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 1105,63</t>
+          <t>-53,71; 927,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,32; inf</t>
+          <t>-29,64; 1276,63</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2,86</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5,02</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>3,51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,86</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>3,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 10,91</t>
+          <t>0,62; 7,15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,15</t>
+          <t>0,93; 7,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 7,82</t>
+          <t>1,31; 11,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,92</t>
+          <t>-1,5; 10,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,66</t>
+          <t>-3,85; 3,11</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,81</t>
+          <t>-2,5; 8,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,36</t>
+          <t>0,18; 6,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,09</t>
+          <t>-0,93; 3,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,4</t>
+          <t>0,14; 7,81</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>188,24%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-44,11%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>59,91%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>309,31%</t>
+          <t>340,03%</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,45; —</t>
+          <t>-56,68; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,86; —</t>
+          <t>-66,17; —</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,58</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,71</t>
+          <t>-0,4; 1,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,39</t>
+          <t>-0,06; 1,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,06</t>
+          <t>1,23; 3,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,21</t>
+          <t>0,56; 2,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,86</t>
+          <t>-0,45; 1,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,63</t>
+          <t>1,42; 4,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,65</t>
+          <t>0,26; 1,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,3</t>
+          <t>0,01; 1,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,31</t>
+          <t>1,67; 3,6</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>101,09%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>291,59%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>187,14%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>53,14%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>293,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>101,09%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>273,45%</t>
+          <t>331,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>282,64%</t>
+          <t>310,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>21,43; 619,96</t>
+          <t>-40,09; 249,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 342,36</t>
+          <t>-11,84; 419,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>76,01; 914,07</t>
+          <t>87,5; 821,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,28; 264,34</t>
+          <t>23,61; 593,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 384,07</t>
+          <t>-40,81; 295,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>75,66; 721,89</t>
+          <t>94,75; 862,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,29; 309,47</t>
+          <t>17,89; 300,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 225,62</t>
+          <t>-1,59; 246,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>118,77; 538,56</t>
+          <t>136,73; 605,17</t>
         </is>
       </c>
     </row>
